--- a/output/five-decade-tables/ppbr_by_group.xlsx
+++ b/output/five-decade-tables/ppbr_by_group.xlsx
@@ -408,22 +408,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.605259272443536</v>
+        <v>1.605259272443549</v>
       </c>
       <c r="D2">
-        <v>1.385040605560643</v>
+        <v>1.385040605560672</v>
       </c>
       <c r="E2">
-        <v>1.365724182779859</v>
+        <v>1.365724182779856</v>
       </c>
       <c r="F2">
-        <v>1.397949369188232</v>
+        <v>1.397949369188221</v>
       </c>
       <c r="G2">
-        <v>1.209916648118828</v>
+        <v>1.209916648118826</v>
       </c>
       <c r="H2">
-        <v>1.188879882358178</v>
+        <v>1.188879882358196</v>
       </c>
     </row>
     <row r="4">
@@ -448,19 +448,19 @@
         <v>2.805696231723631</v>
       </c>
       <c r="D5">
-        <v>2.065987816108237</v>
+        <v>2.065987816108238</v>
       </c>
       <c r="E5">
         <v>1.798234756909698</v>
       </c>
       <c r="F5">
-        <v>1.741842954466939</v>
+        <v>1.741842954466937</v>
       </c>
       <c r="G5">
         <v>1.407029264112328</v>
       </c>
       <c r="H5">
-        <v>1.388949660345186</v>
+        <v>1.388949660345183</v>
       </c>
     </row>
     <row r="6">
@@ -478,19 +478,19 @@
         <v>1.886971443296558</v>
       </c>
       <c r="D6">
-        <v>1.939783584284483</v>
+        <v>1.939783584284481</v>
       </c>
       <c r="E6">
-        <v>2.061889745292506</v>
+        <v>2.061889745292504</v>
       </c>
       <c r="F6">
-        <v>1.923276961778023</v>
+        <v>1.923276961778024</v>
       </c>
       <c r="G6">
-        <v>1.391869557068534</v>
+        <v>1.391869557068537</v>
       </c>
       <c r="H6">
-        <v>1.33683096691496</v>
+        <v>1.336830966914963</v>
       </c>
     </row>
     <row r="7">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>2.11021988174427</v>
+        <v>2.110219881744261</v>
       </c>
       <c r="D7">
-        <v>1.719003589509293</v>
+        <v>1.719003589509284</v>
       </c>
       <c r="E7">
-        <v>1.61568507799319</v>
+        <v>1.615685077993188</v>
       </c>
       <c r="F7">
-        <v>1.556022605997361</v>
+        <v>1.556022605997366</v>
       </c>
       <c r="G7">
-        <v>1.273279697315301</v>
+        <v>1.273279697315299</v>
       </c>
       <c r="H7">
-        <v>1.241791687492023</v>
+        <v>1.241791687492027</v>
       </c>
     </row>
     <row r="8">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>2.358565995351092</v>
+        <v>2.358565995351106</v>
       </c>
       <c r="D8">
-        <v>2.111712908508027</v>
+        <v>2.111712908508035</v>
       </c>
       <c r="E8">
-        <v>2.41074621109758</v>
+        <v>2.410746211097572</v>
       </c>
       <c r="F8">
-        <v>2.504363892587292</v>
+        <v>2.504363892587298</v>
       </c>
       <c r="G8">
-        <v>1.696110291877406</v>
+        <v>1.696110291877412</v>
       </c>
       <c r="H8">
-        <v>1.561715226552278</v>
+        <v>1.561715226552275</v>
       </c>
     </row>
     <row r="9">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.496169532910847</v>
+        <v>1.496169532910815</v>
       </c>
       <c r="D9">
-        <v>1.260411152325242</v>
+        <v>1.260411152325284</v>
       </c>
       <c r="E9">
-        <v>1.174864596592528</v>
+        <v>1.174864596592512</v>
       </c>
       <c r="F9">
-        <v>1.13292998460476</v>
+        <v>1.132929984604769</v>
       </c>
       <c r="G9">
-        <v>1.052923237052778</v>
+        <v>1.052923237052765</v>
       </c>
       <c r="H9">
-        <v>1.038159600975639</v>
+        <v>1.038159600975643</v>
       </c>
     </row>
     <row r="10">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>2.053756015902909</v>
+        <v>2.05375601590291</v>
       </c>
       <c r="D10">
         <v>1.603989361702128</v>
       </c>
       <c r="E10">
-        <v>1.991368126623305</v>
+        <v>1.991368126623304</v>
       </c>
       <c r="F10">
         <v>1.660523727836594</v>
@@ -610,7 +610,7 @@
         <v>1.434610254332598</v>
       </c>
       <c r="H10">
-        <v>1.318234063021959</v>
+        <v>1.318234063021958</v>
       </c>
     </row>
     <row r="11">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="F11">
-        <v>1.553744752435086</v>
+        <v>1.553744752435085</v>
       </c>
       <c r="G11">
-        <v>1.305101956951458</v>
+        <v>1.305101956951459</v>
       </c>
       <c r="H11">
-        <v>1.249895606486741</v>
+        <v>1.24989560648674</v>
       </c>
     </row>
     <row r="13">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C14">
-        <v>1.448970661967231</v>
+        <v>1.661357834887111</v>
       </c>
       <c r="D14">
-        <v>1.300132320020576</v>
+        <v>1.422404169346311</v>
       </c>
       <c r="E14">
-        <v>1.31133826929285</v>
+        <v>1.444920606147754</v>
       </c>
       <c r="F14">
-        <v>1.357192164224475</v>
+        <v>1.483734392207943</v>
       </c>
       <c r="G14">
-        <v>1.164936670683428</v>
+        <v>1.265752816410149</v>
       </c>
       <c r="H14">
-        <v>1.145074627541307</v>
+        <v>1.192847439194354</v>
       </c>
     </row>
     <row r="15">
@@ -683,22 +683,22 @@
         </is>
       </c>
       <c r="C15">
-        <v>1.373117051057413</v>
+        <v>1.630645271810919</v>
       </c>
       <c r="D15">
-        <v>1.168544388816842</v>
+        <v>1.409434849150369</v>
       </c>
       <c r="E15">
-        <v>1.092051603444085</v>
+        <v>1.388042680153873</v>
       </c>
       <c r="F15">
-        <v>1.070256304419272</v>
+        <v>1.441765282038936</v>
       </c>
       <c r="G15">
-        <v>0.9686485680607748</v>
+        <v>1.224143872694104</v>
       </c>
       <c r="H15">
-        <v>0.9866492779858989</v>
+        <v>1.215529022564628</v>
       </c>
     </row>
     <row r="16">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="C16">
-        <v>1.25666595478778</v>
+        <v>1.515230375470672</v>
       </c>
       <c r="D16">
-        <v>1.078830418199842</v>
+        <v>1.330673039700353</v>
       </c>
       <c r="E16">
-        <v>0.9783594641211856</v>
+        <v>1.303503596270055</v>
       </c>
       <c r="F16">
-        <v>0.9899130065511024</v>
+        <v>1.339613118627704</v>
       </c>
       <c r="G16">
-        <v>0.9145083605519762</v>
+        <v>1.173552156620491</v>
       </c>
       <c r="H16">
-        <v>0.9384306615857892</v>
+        <v>1.193804556958014</v>
       </c>
     </row>
     <row r="17">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>1.140409289761884</v>
+        <v>1.412257995863231</v>
       </c>
       <c r="D17">
-        <v>0.9937194461034812</v>
+        <v>1.261461690777797</v>
       </c>
       <c r="E17">
-        <v>0.9136455629456736</v>
+        <v>1.194721283851641</v>
       </c>
       <c r="F17">
-        <v>0.9080502679899192</v>
+        <v>1.210480221581268</v>
       </c>
       <c r="G17">
-        <v>0.8539895655766644</v>
+        <v>1.088221520620491</v>
       </c>
       <c r="H17">
-        <v>0.8792711558946436</v>
+        <v>1.136341803393238</v>
       </c>
     </row>
     <row r="19">
@@ -780,22 +780,22 @@
         </is>
       </c>
       <c r="C20">
-        <v>1.4744957045285</v>
+        <v>1.474495704528579</v>
       </c>
       <c r="D20">
-        <v>1.275835493095224</v>
+        <v>1.275835493095244</v>
       </c>
       <c r="E20">
-        <v>1.192216374079861</v>
+        <v>1.19221637407985</v>
       </c>
       <c r="F20">
-        <v>1.205964871869065</v>
+        <v>1.205964871869097</v>
       </c>
       <c r="G20">
-        <v>1.06938227777683</v>
+        <v>1.069382277776815</v>
       </c>
       <c r="H20">
-        <v>1.059059145148582</v>
+        <v>1.059059145148564</v>
       </c>
     </row>
     <row r="21">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="C21">
-        <v>1.869833165205632</v>
+        <v>1.869833165205638</v>
       </c>
       <c r="D21">
-        <v>1.637906509096493</v>
+        <v>1.637906509096497</v>
       </c>
       <c r="E21">
-        <v>1.734552208748138</v>
+        <v>1.734552208748146</v>
       </c>
       <c r="F21">
-        <v>1.829215225843285</v>
+        <v>1.829215225843298</v>
       </c>
       <c r="G21">
-        <v>1.496296580151941</v>
+        <v>1.496296580151956</v>
       </c>
       <c r="H21">
-        <v>1.456285437624011</v>
+        <v>1.456285437624019</v>
       </c>
     </row>
     <row r="23">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C24">
-        <v>1.606595723255613</v>
+        <v>1.606595723255617</v>
       </c>
       <c r="D24">
-        <v>1.357818635725151</v>
+        <v>1.357818635725133</v>
       </c>
       <c r="E24">
-        <v>1.29187616183193</v>
+        <v>1.291876161831936</v>
       </c>
       <c r="F24">
-        <v>1.288856233407922</v>
+        <v>1.288856233407893</v>
       </c>
       <c r="G24">
-        <v>1.159256785961344</v>
+        <v>1.159256785961351</v>
       </c>
       <c r="H24">
-        <v>1.148392904509075</v>
+        <v>1.148392904509086</v>
       </c>
     </row>
     <row r="25">
@@ -877,22 +877,22 @@
         </is>
       </c>
       <c r="C25">
-        <v>1.580699720295309</v>
+        <v>1.580699720295292</v>
       </c>
       <c r="D25">
-        <v>1.763682424455052</v>
+        <v>1.763682424455047</v>
       </c>
       <c r="E25">
-        <v>2.138262576194852</v>
+        <v>2.138262576194854</v>
       </c>
       <c r="F25">
-        <v>2.207869495579715</v>
+        <v>2.207869495579712</v>
       </c>
       <c r="G25">
-        <v>1.525569679769176</v>
+        <v>1.525569679769179</v>
       </c>
       <c r="H25">
-        <v>1.420255485042034</v>
+        <v>1.420255485042046</v>
       </c>
     </row>
   </sheetData>
